--- a/docs/보고서/임태형_프로젝트활동_정리.xlsx
+++ b/docs/보고서/임태형_프로젝트활동_정리.xlsx
@@ -533,7 +533,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>156개 (전체 브랜치, 이메일 기준; git stash WIP/index 2건 제외)</t>
+          <t>161개 (전체 브랜치, 이메일 기준; git stash WIP/index 2건 제외)</t>
         </is>
       </c>
     </row>
@@ -545,7 +545,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-05-29 ~ 2026-07-07 (월별 분포: 5월 2건 / 6월 115건 / 7월 39건)</t>
+          <t>2026-05-29 ~ 2026-07-07 (월별 분포: 5월 2건 / 6월 115건 / 7월 44건)</t>
         </is>
       </c>
     </row>
@@ -572,7 +572,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>인증/로그인(이메일·소셜 로그인, 콜백 처리), 중고거래 글쓰기/목록 초기 구현, 방렌트 목록 초기 구현, 이미지 업로드 공통 훅/컴포넌트화, 관리자 대시보드·신고관리 시스템 전체 구축, 안전결제(Xendit) 전체 구현, 채팅 부가기능(안전결제 배너·리뷰·신고/차단), Kanto GO!(번개모임) 기능 전체 구현, AI 이미지 업로드 검수, 성능 감사/개선</t>
+          <t>인증/로그인(이메일·소셜 로그인, 콜백 처리), 중고거래 글쓰기/목록 초기 구현, 방렌트 목록 초기 구현, 이미지 업로드 공통 훅/컴포넌트화, 관리자 대시보드·신고관리 시스템 전체 구축, 안전결제(Xendit) 전체 구현, 채팅 부가기능(안전결제 배너·리뷰·신고/차단), Kanto GO!(번개모임) 기능 전체 구현, AI 이미지 업로드 검수, 성능 감사/개선  |  [설계·의사결정 기여] ① CLAUDE.md(Claude Code 협업 가이드라인) 최초 도입·푸시(06/17). ② Supabase Storage 이미지 저장 구조 설계 — 단일 images 버킷에서 프로필은 avatars/{userId}/…, 게시글은 {userId}/{postId}/{timestamp} 경로로 사용자·게시글 이미지를 분리. ③ 필리핀 바랑가이(barangay) 단위 지역 세분화 제안 — city 하위 barangay까지 세분화해 목록 카드·필터에서 사용자가 지역을 더 구체적으로 확인·검색.</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F157"/>
+  <dimension ref="A1:F162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5368,6 +5368,166 @@
       <c r="F157" t="inlineStr">
         <is>
           <t>Merge pull request #631 from FRONTENDBOOTCAMP-17th/hotfix/v.1.3.2 (4-2차 배포 핫픽스 통합)</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>2026-07-07 15:54</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>874496a157</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>fix(수정)</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>성능 최적화</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>fix: 목록 이미지 402 에러 해결 (Vercel 이미지 최적화 우회)</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>2026-07-07 16:07</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>1a684442e3</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>병합/기타</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>성능 최적화</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Merge pull request #646 from FRONTENDBOOTCAMP-17th/hotfix/v1.3.3 (이미지 402 핫픽스)</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>2026-07-07 16:23</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>123ebeafdf</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>fix(수정)</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>성능 최적화</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>fix: 이미지 402 에러 전역 해결 (next.config images.unoptimized)</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>2026-07-07 16:38</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>147331bfd1</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>병합/기타</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>성능 최적화</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Merge pull request #650 from FRONTENDBOOTCAMP-17th/hotfix/v1.3.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>2026-07-07 17:06</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>55e72e269f</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>병합/기타</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>기타/버그수정</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Merge branch 'develop' into reports/v1.3.0</t>
         </is>
       </c>
     </row>
@@ -5410,7 +5570,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3">
@@ -5600,7 +5760,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -5651,7 +5811,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3">
@@ -5661,7 +5821,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
@@ -5746,7 +5906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6332,13 +6492,31 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>#650</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>hotfix/v1.3.3 (이미지 402)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>목록·전역 이미지 402 에러 해결 (Vercel 최적화 우회 + next.config unoptimized)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36"/>
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>참고</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>관리자 신고 관리 페이지, 결제/Xendit/안전결제 UI, 거래완료 후기 작성, 채팅방 유저 신고/차단, 신고-제재 FK 정합성, kantoGo 그룹채팅, AI 이미지 검수, 상세페이지 지도 추가, 목록페이지 UI/필터 개편 등은 develop에 직접 커밋되거나 이후 다른 팀원이 최종 병합해, 위 목록에는 없지만 임태형의 실제 기여로 인정됩니다. 반대로 #71/#185/#197/#205/#207/#209/#212/#252/#284/#289/#292/#295/#345/#403/#407/#409/#433/#435/#437/#438/#440/#478/#503/#512/#555/#571/#583/#598/#609/#627/#631 등은 병합만 수행했고 실작업은 soyu/dongkeun/DoHyuk/urstory 등 타 팀원이 진행했습니다.</t>
         </is>
